--- a/data/nzd0118/nzd0118.xlsx
+++ b/data/nzd0118/nzd0118.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I314"/>
+  <dimension ref="A1:I316"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10788,6 +10788,72 @@
         <v>387.37</v>
       </c>
       <c r="I314" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:05:11+00:00</t>
+        </is>
+      </c>
+      <c r="B315" t="n">
+        <v>374.03</v>
+      </c>
+      <c r="C315" t="n">
+        <v>374.83</v>
+      </c>
+      <c r="D315" t="n">
+        <v>381.42</v>
+      </c>
+      <c r="E315" t="n">
+        <v>378.35</v>
+      </c>
+      <c r="F315" t="n">
+        <v>375.66</v>
+      </c>
+      <c r="G315" t="n">
+        <v>378.78</v>
+      </c>
+      <c r="H315" t="n">
+        <v>385.13</v>
+      </c>
+      <c r="I315" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:05:24+00:00</t>
+        </is>
+      </c>
+      <c r="B316" t="n">
+        <v>374.46</v>
+      </c>
+      <c r="C316" t="n">
+        <v>375.3</v>
+      </c>
+      <c r="D316" t="n">
+        <v>381.04</v>
+      </c>
+      <c r="E316" t="n">
+        <v>378.26</v>
+      </c>
+      <c r="F316" t="n">
+        <v>375.65</v>
+      </c>
+      <c r="G316" t="n">
+        <v>379.39</v>
+      </c>
+      <c r="H316" t="n">
+        <v>385.12</v>
+      </c>
+      <c r="I316" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -10804,7 +10870,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B328"/>
+  <dimension ref="A1:B330"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14087,6 +14153,26 @@
       </c>
       <c r="B328" t="n">
         <v>-0.7</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B329" t="n">
+        <v>-0.87</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B330" t="n">
+        <v>-0.3</v>
       </c>
     </row>
   </sheetData>
@@ -14255,28 +14341,28 @@
         <v>0.0478</v>
       </c>
       <c r="I2" t="n">
-        <v>0.07120857464323423</v>
+        <v>0.05471355857597909</v>
       </c>
       <c r="J2" t="n">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="K2" t="n">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="L2" t="n">
-        <v>0.00558301398496952</v>
+        <v>0.003275811850191546</v>
       </c>
       <c r="M2" t="n">
-        <v>5.514065358411499</v>
+        <v>5.537688551935134</v>
       </c>
       <c r="N2" t="n">
-        <v>46.15416196777161</v>
+        <v>46.88369439663286</v>
       </c>
       <c r="O2" t="n">
-        <v>6.793685448103379</v>
+        <v>6.847166888329279</v>
       </c>
       <c r="P2" t="n">
-        <v>385.142224207358</v>
+        <v>385.3300544615792</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -14333,28 +14419,28 @@
         <v>0.0731</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1010129834932123</v>
+        <v>0.09084517888962525</v>
       </c>
       <c r="J3" t="n">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="K3" t="n">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02106670619941298</v>
+        <v>0.01706701073039008</v>
       </c>
       <c r="M3" t="n">
-        <v>4.023989575341389</v>
+        <v>4.041530291980202</v>
       </c>
       <c r="N3" t="n">
-        <v>24.23021812161329</v>
+        <v>24.46504800898339</v>
       </c>
       <c r="O3" t="n">
-        <v>4.922419945678476</v>
+        <v>4.946215523911528</v>
       </c>
       <c r="P3" t="n">
-        <v>380.2525453708211</v>
+        <v>380.368325726297</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -14411,28 +14497,28 @@
         <v>0.0895</v>
       </c>
       <c r="I4" t="n">
-        <v>0.00147653100821703</v>
+        <v>-0.005360384231224725</v>
       </c>
       <c r="J4" t="n">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="K4" t="n">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="L4" t="n">
-        <v>4.608537881645169e-06</v>
+        <v>6.11195201404291e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>3.96566913389906</v>
+        <v>3.971293165882577</v>
       </c>
       <c r="N4" t="n">
-        <v>24.17499798885983</v>
+        <v>24.19698276669885</v>
       </c>
       <c r="O4" t="n">
-        <v>4.91680770305895</v>
+        <v>4.919042870996232</v>
       </c>
       <c r="P4" t="n">
-        <v>386.4971480524543</v>
+        <v>386.5750043264006</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -14489,28 +14575,28 @@
         <v>0.0728</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.00505383234386141</v>
+        <v>-0.01239271113157773</v>
       </c>
       <c r="J5" t="n">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="K5" t="n">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="L5" t="n">
-        <v>3.72838012223653e-05</v>
+        <v>0.0002258768141775169</v>
       </c>
       <c r="M5" t="n">
-        <v>4.889411659672857</v>
+        <v>4.889216444277787</v>
       </c>
       <c r="N5" t="n">
-        <v>35.38837092406652</v>
+        <v>35.36941647365721</v>
       </c>
       <c r="O5" t="n">
-        <v>5.948812564206954</v>
+        <v>5.947219221926934</v>
       </c>
       <c r="P5" t="n">
-        <v>384.191942754875</v>
+        <v>384.2749354775864</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -14567,28 +14653,28 @@
         <v>0.0607</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1641926428043986</v>
+        <v>-0.1761202802865276</v>
       </c>
       <c r="J6" t="n">
+        <v>315</v>
+      </c>
+      <c r="K6" t="n">
         <v>313</v>
       </c>
-      <c r="K6" t="n">
-        <v>311</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.03956739622838934</v>
+        <v>0.0451630886284109</v>
       </c>
       <c r="M6" t="n">
-        <v>4.733117103866118</v>
+        <v>4.753692626208713</v>
       </c>
       <c r="N6" t="n">
-        <v>32.91858647678468</v>
+        <v>33.23057321932014</v>
       </c>
       <c r="O6" t="n">
-        <v>5.737472132985456</v>
+        <v>5.764596535692688</v>
       </c>
       <c r="P6" t="n">
-        <v>389.179442677944</v>
+        <v>389.3165341833986</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -14645,28 +14731,28 @@
         <v>0.0832</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1077425403684232</v>
+        <v>-0.1147274126631533</v>
       </c>
       <c r="J7" t="n">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="K7" t="n">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02348215006672694</v>
+        <v>0.02670087247539887</v>
       </c>
       <c r="M7" t="n">
-        <v>4.075872432292561</v>
+        <v>4.081828375040451</v>
       </c>
       <c r="N7" t="n">
-        <v>24.642655702796</v>
+        <v>24.66946950290904</v>
       </c>
       <c r="O7" t="n">
-        <v>4.964136954476175</v>
+        <v>4.966836971645943</v>
       </c>
       <c r="P7" t="n">
-        <v>387.3861896815337</v>
+        <v>387.4657682746188</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -14723,28 +14809,28 @@
         <v>0.079</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.202598982813024</v>
+        <v>-0.2067329218257666</v>
       </c>
       <c r="J8" t="n">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="K8" t="n">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="L8" t="n">
-        <v>0.05366024505585731</v>
+        <v>0.05637671283352041</v>
       </c>
       <c r="M8" t="n">
-        <v>5.062089733228182</v>
+        <v>5.049783239148605</v>
       </c>
       <c r="N8" t="n">
-        <v>36.9521501662467</v>
+        <v>36.78093081051495</v>
       </c>
       <c r="O8" t="n">
-        <v>6.078828025717351</v>
+        <v>6.064728420178017</v>
       </c>
       <c r="P8" t="n">
-        <v>393.7497451217044</v>
+        <v>393.7968454870544</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -14782,7 +14868,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I314"/>
+  <dimension ref="A1:I316"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29515,6 +29601,100 @@
         </is>
       </c>
     </row>
+    <row r="315">
+      <c r="A315" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:05:11+00:00</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>-36.168587546357415,175.48431749919425</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>-36.16867917327431,175.485208502761</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>-36.168718410488246,175.48608672292252</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>-36.16871519080042,175.48695350129364</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>-36.168659671580606,175.48783442145893</t>
+        </is>
+      </c>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>-36.16847314997714,175.4886818232541</t>
+        </is>
+      </c>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>-36.168206541945146,175.4895114181914</t>
+        </is>
+      </c>
+      <c r="I315" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:05:24+00:00</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>-36.16858369994553,175.48431807211324</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>-36.16867496905553,175.48520912894398</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>-36.16872183286055,175.4860865987988</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>-36.16871599795419,175.48695359746736</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>-36.168659760099665,175.48783444219237</t>
+        </is>
+      </c>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>-36.16846786969596,175.48867994207956</t>
+        </is>
+      </c>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>-36.16820662755311,175.48951145284477</t>
+        </is>
+      </c>
+      <c r="I316" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0118/nzd0118.xlsx
+++ b/data/nzd0118/nzd0118.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I316"/>
+  <dimension ref="A1:I317"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10856,6 +10856,39 @@
       <c r="I316" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:05:16+00:00</t>
+        </is>
+      </c>
+      <c r="B317" t="n">
+        <v>376.32</v>
+      </c>
+      <c r="C317" t="n">
+        <v>377.06</v>
+      </c>
+      <c r="D317" t="n">
+        <v>382.61</v>
+      </c>
+      <c r="E317" t="n">
+        <v>379.68</v>
+      </c>
+      <c r="F317" t="n">
+        <v>377.24</v>
+      </c>
+      <c r="G317" t="n">
+        <v>380.95</v>
+      </c>
+      <c r="H317" t="n">
+        <v>386.9</v>
+      </c>
+      <c r="I317" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -10870,7 +10903,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B330"/>
+  <dimension ref="A1:B331"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14173,6 +14206,16 @@
       </c>
       <c r="B330" t="n">
         <v>-0.3</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B331" t="n">
+        <v>0.31</v>
       </c>
     </row>
   </sheetData>
@@ -14341,28 +14384,28 @@
         <v>0.0478</v>
       </c>
       <c r="I2" t="n">
-        <v>0.05471355857597909</v>
+        <v>0.0480019950813442</v>
       </c>
       <c r="J2" t="n">
+        <v>316</v>
+      </c>
+      <c r="K2" t="n">
         <v>315</v>
       </c>
-      <c r="K2" t="n">
-        <v>314</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.003275811850191546</v>
+        <v>0.002521741157515023</v>
       </c>
       <c r="M2" t="n">
-        <v>5.537688551935134</v>
+        <v>5.544373424417533</v>
       </c>
       <c r="N2" t="n">
-        <v>46.88369439663286</v>
+        <v>47.07988750287513</v>
       </c>
       <c r="O2" t="n">
-        <v>6.847166888329279</v>
+        <v>6.861478521636218</v>
       </c>
       <c r="P2" t="n">
-        <v>385.3300544615792</v>
+        <v>385.4066198114425</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -14419,28 +14462,28 @@
         <v>0.0731</v>
       </c>
       <c r="I3" t="n">
-        <v>0.09084517888962525</v>
+        <v>0.08716374868596616</v>
       </c>
       <c r="J3" t="n">
+        <v>316</v>
+      </c>
+      <c r="K3" t="n">
         <v>315</v>
       </c>
-      <c r="K3" t="n">
-        <v>314</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.01706701073039008</v>
+        <v>0.01577145425283477</v>
       </c>
       <c r="M3" t="n">
-        <v>4.041530291980202</v>
+        <v>4.044323174893599</v>
       </c>
       <c r="N3" t="n">
-        <v>24.46504800898339</v>
+        <v>24.49119207291713</v>
       </c>
       <c r="O3" t="n">
-        <v>4.946215523911528</v>
+        <v>4.948857653329416</v>
       </c>
       <c r="P3" t="n">
-        <v>380.368325726297</v>
+        <v>380.4103233907408</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -14497,28 +14540,28 @@
         <v>0.0895</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.005360384231224725</v>
+        <v>-0.007807687723158064</v>
       </c>
       <c r="J4" t="n">
+        <v>316</v>
+      </c>
+      <c r="K4" t="n">
         <v>315</v>
       </c>
-      <c r="K4" t="n">
-        <v>314</v>
-      </c>
       <c r="L4" t="n">
-        <v>6.11195201404291e-05</v>
+        <v>0.0001302856696321353</v>
       </c>
       <c r="M4" t="n">
-        <v>3.971293165882577</v>
+        <v>3.969868570816024</v>
       </c>
       <c r="N4" t="n">
-        <v>24.19698276669885</v>
+        <v>24.16604293346037</v>
       </c>
       <c r="O4" t="n">
-        <v>4.919042870996232</v>
+        <v>4.915896961233054</v>
       </c>
       <c r="P4" t="n">
-        <v>386.5750043264006</v>
+        <v>386.60292310393</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -14575,28 +14618,28 @@
         <v>0.0728</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.01239271113157773</v>
+        <v>-0.01510097085228277</v>
       </c>
       <c r="J5" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="K5" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0002258768141775169</v>
+        <v>0.0003370568002435403</v>
       </c>
       <c r="M5" t="n">
-        <v>4.889216444277787</v>
+        <v>4.885053294631281</v>
       </c>
       <c r="N5" t="n">
-        <v>35.36941647365721</v>
+        <v>35.31455179548298</v>
       </c>
       <c r="O5" t="n">
-        <v>5.947219221926934</v>
+        <v>5.942604798864129</v>
       </c>
       <c r="P5" t="n">
-        <v>384.2749354775864</v>
+        <v>384.3056181589142</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -14653,28 +14696,28 @@
         <v>0.0607</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1761202802865276</v>
+        <v>-0.1809010640883934</v>
       </c>
       <c r="J6" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="K6" t="n">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0451630886284109</v>
+        <v>0.04760392591040141</v>
       </c>
       <c r="M6" t="n">
-        <v>4.753692626208713</v>
+        <v>4.759103603472172</v>
       </c>
       <c r="N6" t="n">
-        <v>33.23057321932014</v>
+        <v>33.29569684741309</v>
       </c>
       <c r="O6" t="n">
-        <v>5.764596535692688</v>
+        <v>5.770242356037837</v>
       </c>
       <c r="P6" t="n">
-        <v>389.3165341833986</v>
+        <v>389.3715811032824</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -14731,28 +14774,28 @@
         <v>0.0832</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1147274126631533</v>
+        <v>-0.1169347261122069</v>
       </c>
       <c r="J7" t="n">
+        <v>316</v>
+      </c>
+      <c r="K7" t="n">
         <v>315</v>
       </c>
-      <c r="K7" t="n">
-        <v>314</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.02670087247539887</v>
+        <v>0.02785021961946565</v>
       </c>
       <c r="M7" t="n">
-        <v>4.081828375040451</v>
+        <v>4.078989458202187</v>
       </c>
       <c r="N7" t="n">
-        <v>24.66946950290904</v>
+        <v>24.62840558341424</v>
       </c>
       <c r="O7" t="n">
-        <v>4.966836971645943</v>
+        <v>4.962701440084245</v>
       </c>
       <c r="P7" t="n">
-        <v>387.4657682746188</v>
+        <v>387.4909631575179</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -14809,28 +14852,28 @@
         <v>0.079</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2067329218257666</v>
+        <v>-0.2076064709991303</v>
       </c>
       <c r="J8" t="n">
+        <v>316</v>
+      </c>
+      <c r="K8" t="n">
         <v>315</v>
       </c>
-      <c r="K8" t="n">
-        <v>314</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.05637671283352041</v>
+        <v>0.0571800282196796</v>
       </c>
       <c r="M8" t="n">
-        <v>5.049783239148605</v>
+        <v>5.038065859988794</v>
       </c>
       <c r="N8" t="n">
-        <v>36.78093081051495</v>
+        <v>36.67000032955215</v>
       </c>
       <c r="O8" t="n">
-        <v>6.064728420178017</v>
+        <v>6.055575970091709</v>
       </c>
       <c r="P8" t="n">
-        <v>393.7968454870544</v>
+        <v>393.8068164176166</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -14868,7 +14911,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I316"/>
+  <dimension ref="A1:I317"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29695,6 +29738,53 @@
         </is>
       </c>
     </row>
+    <row r="317">
+      <c r="A317" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:05:16+00:00</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>-36.16856706197782,175.48432055032038</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>-36.168659225597914,175.4852114737989</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>-36.168707693059226,175.48608711162575</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>-36.16870326286139,175.4869520800603</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>-36.16864568557101,175.48783114557042</t>
+        </is>
+      </c>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>-36.168454366025884,175.48867513120817</t>
+        </is>
+      </c>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>-36.168191389334595,175.4895052845432</t>
+        </is>
+      </c>
+      <c r="I317" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0118/nzd0118.xlsx
+++ b/data/nzd0118/nzd0118.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I317"/>
+  <dimension ref="A1:I318"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10889,6 +10889,39 @@
       <c r="I317" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:05:36+00:00</t>
+        </is>
+      </c>
+      <c r="B318" t="n">
+        <v>378.1</v>
+      </c>
+      <c r="C318" t="n">
+        <v>377.41</v>
+      </c>
+      <c r="D318" t="n">
+        <v>381.46</v>
+      </c>
+      <c r="E318" t="n">
+        <v>379.23</v>
+      </c>
+      <c r="F318" t="n">
+        <v>376.63</v>
+      </c>
+      <c r="G318" t="n">
+        <v>380.83</v>
+      </c>
+      <c r="H318" t="n">
+        <v>387.38</v>
+      </c>
+      <c r="I318" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -10903,7 +10936,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B331"/>
+  <dimension ref="A1:B332"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14216,6 +14249,16 @@
       </c>
       <c r="B331" t="n">
         <v>0.31</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B332" t="n">
+        <v>0.85</v>
       </c>
     </row>
   </sheetData>
@@ -14384,28 +14427,28 @@
         <v>0.0478</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0480019950813442</v>
+        <v>0.042493293976104</v>
       </c>
       <c r="J2" t="n">
+        <v>317</v>
+      </c>
+      <c r="K2" t="n">
         <v>316</v>
       </c>
-      <c r="K2" t="n">
-        <v>315</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.002521741157515023</v>
+        <v>0.001980903639176579</v>
       </c>
       <c r="M2" t="n">
-        <v>5.544373424417533</v>
+        <v>5.546420466962805</v>
       </c>
       <c r="N2" t="n">
-        <v>47.07988750287513</v>
+        <v>47.16235825036264</v>
       </c>
       <c r="O2" t="n">
-        <v>6.861478521636218</v>
+        <v>6.867485584285025</v>
       </c>
       <c r="P2" t="n">
-        <v>385.4066198114425</v>
+        <v>385.4697467714111</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -14462,28 +14505,28 @@
         <v>0.0731</v>
       </c>
       <c r="I3" t="n">
-        <v>0.08716374868596616</v>
+        <v>0.08374089365998653</v>
       </c>
       <c r="J3" t="n">
+        <v>317</v>
+      </c>
+      <c r="K3" t="n">
         <v>316</v>
       </c>
-      <c r="K3" t="n">
-        <v>315</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.01577145425283477</v>
+        <v>0.01461968908065725</v>
       </c>
       <c r="M3" t="n">
-        <v>4.044323174893599</v>
+        <v>4.045831507609601</v>
       </c>
       <c r="N3" t="n">
-        <v>24.49119207291713</v>
+        <v>24.50304976723433</v>
       </c>
       <c r="O3" t="n">
-        <v>4.948857653329416</v>
+        <v>4.95005553173238</v>
       </c>
       <c r="P3" t="n">
-        <v>380.4103233907408</v>
+        <v>380.4495475976954</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -14540,28 +14583,28 @@
         <v>0.0895</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.007807687723158064</v>
+        <v>-0.01097094832943426</v>
       </c>
       <c r="J4" t="n">
+        <v>317</v>
+      </c>
+      <c r="K4" t="n">
         <v>316</v>
       </c>
-      <c r="K4" t="n">
-        <v>315</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.0001302856696321353</v>
+        <v>0.0002581384254890517</v>
       </c>
       <c r="M4" t="n">
-        <v>3.969868570816024</v>
+        <v>3.971725931483864</v>
       </c>
       <c r="N4" t="n">
-        <v>24.16604293346037</v>
+        <v>24.16588896849536</v>
       </c>
       <c r="O4" t="n">
-        <v>4.915896961233054</v>
+        <v>4.91588130130248</v>
       </c>
       <c r="P4" t="n">
-        <v>386.60292310393</v>
+        <v>386.6391724886485</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -14618,28 +14661,28 @@
         <v>0.0728</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.01510097085228277</v>
+        <v>-0.01806507718488587</v>
       </c>
       <c r="J5" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="K5" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0003370568002435403</v>
+        <v>0.000484615821937262</v>
       </c>
       <c r="M5" t="n">
-        <v>4.885053294631281</v>
+        <v>4.881843378615011</v>
       </c>
       <c r="N5" t="n">
-        <v>35.31455179548298</v>
+        <v>35.2712170084879</v>
       </c>
       <c r="O5" t="n">
-        <v>5.942604798864129</v>
+        <v>5.938957569177263</v>
       </c>
       <c r="P5" t="n">
-        <v>384.3056181589142</v>
+        <v>384.339352379895</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -14696,28 +14739,28 @@
         <v>0.0607</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1809010640883934</v>
+        <v>-0.1860164878777599</v>
       </c>
       <c r="J6" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="K6" t="n">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="L6" t="n">
-        <v>0.04760392591040141</v>
+        <v>0.05024365043470447</v>
       </c>
       <c r="M6" t="n">
-        <v>4.759103603472172</v>
+        <v>4.76608238412906</v>
       </c>
       <c r="N6" t="n">
-        <v>33.29569684741309</v>
+        <v>33.38489562133665</v>
       </c>
       <c r="O6" t="n">
-        <v>5.770242356037837</v>
+        <v>5.777966391502866</v>
       </c>
       <c r="P6" t="n">
-        <v>389.3715811032824</v>
+        <v>389.4307433981807</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -14774,28 +14817,28 @@
         <v>0.0832</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1169347261122069</v>
+        <v>-0.119189350574419</v>
       </c>
       <c r="J7" t="n">
+        <v>317</v>
+      </c>
+      <c r="K7" t="n">
         <v>316</v>
       </c>
-      <c r="K7" t="n">
-        <v>315</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.02785021961946565</v>
+        <v>0.02904960866194917</v>
       </c>
       <c r="M7" t="n">
-        <v>4.078989458202187</v>
+        <v>4.076278919046799</v>
       </c>
       <c r="N7" t="n">
-        <v>24.62840558341424</v>
+        <v>24.58916969840729</v>
       </c>
       <c r="O7" t="n">
-        <v>4.962701440084245</v>
+        <v>4.958746787083133</v>
       </c>
       <c r="P7" t="n">
-        <v>387.4909631575179</v>
+        <v>387.5168141449033</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -14852,28 +14895,28 @@
         <v>0.079</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2076064709991303</v>
+        <v>-0.2081488022671031</v>
       </c>
       <c r="J8" t="n">
+        <v>317</v>
+      </c>
+      <c r="K8" t="n">
         <v>316</v>
       </c>
-      <c r="K8" t="n">
-        <v>315</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.0571800282196796</v>
+        <v>0.05782687928000829</v>
       </c>
       <c r="M8" t="n">
-        <v>5.038065859988794</v>
+        <v>5.024764128452018</v>
       </c>
       <c r="N8" t="n">
-        <v>36.67000032955215</v>
+        <v>36.55619534117179</v>
       </c>
       <c r="O8" t="n">
-        <v>6.055575970091709</v>
+        <v>6.046171957625071</v>
       </c>
       <c r="P8" t="n">
-        <v>393.8068164176166</v>
+        <v>393.8130346588368</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -14911,7 +14954,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I317"/>
+  <dimension ref="A1:I318"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29785,6 +29828,53 @@
         </is>
       </c>
     </row>
+    <row r="318">
+      <c r="A318" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:05:36+00:00</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>-36.16855113962156,175.48432292193718</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>-36.16865609479668,175.4852119401052</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>-36.168718050238546,175.48608673598815</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>-36.16870729863024,175.48695256092867</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>-36.16865108523296,175.48783241031205</t>
+        </is>
+      </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>-36.168455404769745,175.48867550127514</t>
+        </is>
+      </c>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>-36.168187280152,175.48950362118143</t>
+        </is>
+      </c>
+      <c r="I318" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
